--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -6,11 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2304" yWindow="2304" windowWidth="13716" windowHeight="9960" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="メドレー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="フリー" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="バッタ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="バック" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="フリー" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ブレ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="バッタ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="バック" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,35 +487,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -523,27 +521,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -551,27 +547,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -579,27 +573,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -607,31 +599,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46145</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -643,37 +633,167 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>173.24</v>
+        <v>40.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46172</v>
+        <v>46033</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>193.81</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -688,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -741,7 +861,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -751,7 +871,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -767,7 +887,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -777,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -789,11 +909,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -803,7 +923,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -819,7 +939,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -829,7 +949,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -841,11 +961,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -855,7 +975,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -867,11 +987,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -881,7 +1001,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -889,15 +1009,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -907,7 +1029,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -923,7 +1045,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -933,7 +1055,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -945,11 +1067,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -959,11 +1081,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -971,21 +1093,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1001,35 +1123,217 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>36.55</v>
+        <v>47.95</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
         <v>46207</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>36.89</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E20" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1046,7 +1350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,7 +1387,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1099,7 +1403,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>54.97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1109,7 +1413,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1125,7 +1429,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>48.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1135,7 +1439,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>46033</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1147,11 +1451,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>44.97</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1161,7 +1465,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>46075</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1177,7 +1481,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>44.65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1187,11 +1491,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>46130</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1203,21 +1507,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>47.17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46187</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1225,11 +1529,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>42.92</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1239,339 +1543,25 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46208</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+      <c r="E8" t="n">
+        <v>44.13</v>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>100</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>96.61</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1588,7 +1578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1625,7 +1615,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45823</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1651,7 +1641,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45956</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1667,7 +1657,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.27</v>
+        <v>52.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1677,7 +1667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>46033</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1693,7 +1683,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.97</v>
+        <v>51.07</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1703,7 +1693,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>46075</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1719,7 +1709,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.65</v>
+        <v>50.06</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1729,11 +1719,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46130</v>
+        <v>45956</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1745,21 +1735,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47.17</v>
+        <v>46.12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46187</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1767,11 +1757,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42.92</v>
+        <v>45.67</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1781,25 +1771,77 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
         <v>46208</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>44.13</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E10" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1816,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1853,33 +1895,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>54.97</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1887,25 +1931,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>52.8</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1913,25 +1959,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>51.07</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1939,25 +1987,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>50.06</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45956</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1965,29 +2015,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>46.12</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46145</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1995,47 +2047,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>45.67</v>
+        <v>173.24</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46075</v>
+        <v>46172</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>44.84</v>
+        <v>193.81</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46130</v>
+        <v>46263</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2043,7 +2095,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2051,37 +2103,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>45.97</v>
+        <v>187.87</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46208</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>41.68</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="フリー" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ブレ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="バッタ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="バック" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="バック" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="バッタ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1350,7 +1350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45823</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45956</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.27</v>
+        <v>52.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>46033</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.97</v>
+        <v>51.07</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>46075</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.65</v>
+        <v>50.06</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1491,11 +1491,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46130</v>
+        <v>45956</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47.17</v>
+        <v>46.12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46187</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1529,11 +1529,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42.92</v>
+        <v>45.67</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1543,25 +1543,77 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
         <v>46208</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>44.13</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1578,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1615,33 +1667,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>54.97</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1649,25 +1703,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>52.8</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1675,25 +1731,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>51.07</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1701,25 +1759,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>50.06</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45956</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1727,29 +1787,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>46.12</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46145</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1757,47 +1819,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>45.67</v>
+        <v>173.24</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46075</v>
+        <v>46172</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>44.84</v>
+        <v>193.81</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46130</v>
+        <v>46263</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1805,7 +1867,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1813,37 +1875,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>45.97</v>
+        <v>187.87</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46208</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>41.68</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1895,35 +1931,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>54.97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1931,27 +1965,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>48.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>46033</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1959,27 +1991,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.97</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>46075</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1987,45 +2017,41 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>46130</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+      <c r="E6" t="n">
+        <v>47.17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2035,7 +2061,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46145</v>
+        <v>46187</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2051,17 +2077,17 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>173.24</v>
+        <v>42.92</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46172</v>
+        <v>46208</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2069,25 +2095,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>193.81</v>
+        <v>44.13</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46263</v>
+        <v>46313</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2095,19 +2121,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>187.87</v>
+        <v>40.48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/穂果記録.xlsx
+++ b/穂果記録.xlsx
@@ -6,11 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2304" yWindow="2304" windowWidth="13716" windowHeight="9960" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="フリー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ブレ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="バック" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="バッタ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ブレ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="バッタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.91</v>
+        <v>58.87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47.54</v>
+        <v>55.01</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -551,11 +551,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.48</v>
+        <v>52.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45942</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.39</v>
+        <v>52.97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45942</v>
+        <v>45955</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -603,11 +603,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40.39</v>
+        <v>49.74</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45955</v>
+        <v>45984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -629,11 +629,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>49.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -651,15 +651,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>39.07</v>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1'41"11</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -669,7 +671,7 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46053</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -685,7 +687,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.24</v>
+        <v>47.55</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -695,7 +697,7 @@
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46074</v>
+        <v>46053</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -707,11 +709,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37.73</v>
+        <v>46.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -721,11 +723,11 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -733,21 +735,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40.28</v>
+        <v>47.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -763,35 +765,217 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>36.55</v>
+        <v>47.95</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
         <v>46207</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>36.89</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="C20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -808,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,7 +1045,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.87</v>
+        <v>54.97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -887,7 +1071,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.01</v>
+        <v>52.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -897,7 +1081,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -909,11 +1093,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52.08</v>
+        <v>51.07</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +1107,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45942</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -939,7 +1123,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.97</v>
+        <v>50.06</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -949,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45955</v>
+        <v>45956</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -965,7 +1149,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.74</v>
+        <v>46.12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -991,7 +1175,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.06</v>
+        <v>45.67</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1001,7 +1185,7 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>45984</v>
+        <v>46075</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1009,17 +1193,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1'41"11</t>
-        </is>
+      <c r="E8" t="n">
+        <v>44.84</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1029,11 +1211,11 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46033</v>
+        <v>46130</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1045,21 +1227,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.55</v>
+        <v>45.97</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46053</v>
+        <v>46208</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1067,273 +1249,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>46.9</v>
+        <v>41.68</v>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>95.04000000000001</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>46179</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>100</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>96.61</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1350,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1387,33 +1309,35 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>54.97</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'43"09</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45815</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1421,25 +1345,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>52.8</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'02"71</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1447,25 +1373,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>51.07</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'37"53</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1473,25 +1401,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>50.06</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'21"34</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>45956</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1499,29 +1429,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>46.12</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'14"47</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>45984</v>
+        <v>46145</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1529,47 +1461,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>45.67</v>
+        <v>173.24</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46075</v>
+        <v>46172</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>44.84</v>
+        <v>193.81</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46130</v>
+        <v>46263</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1577,7 +1509,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,37 +1517,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>45.97</v>
+        <v>187.87</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>46208</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小6</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>41.68</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1667,35 +1573,33 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45710</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'43"09</t>
-        </is>
+      <c r="E2" t="n">
+        <v>54.97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45808</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1703,27 +1607,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'02"71</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>48.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>45899</v>
+        <v>46033</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1731,27 +1633,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'37"53</t>
-        </is>
+      <c r="E4" t="n">
+        <v>44.97</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>45991</v>
+        <v>46075</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1759,45 +1659,41 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'21"34</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44.65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46081</v>
+        <v>46130</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小6</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'14"47</t>
-        </is>
+      <c r="E6" t="n">
+        <v>47.17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1807,7 +1703,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46145</v>
+        <v>46187</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1823,17 +1719,17 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>173.24</v>
+        <v>42.92</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46172</v>
+        <v>46208</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1841,25 +1737,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>193.81</v>
+        <v>44.13</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46263</v>
+        <v>46313</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1867,19 +1763,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>187.87</v>
+        <v>40.48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1931,7 +1827,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>45823</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1947,7 +1843,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54.97</v>
+        <v>47.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1957,7 +1853,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>45956</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1973,7 +1869,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.27</v>
+        <v>47.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1983,7 +1879,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>46033</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1999,7 +1895,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44.97</v>
+        <v>44.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2009,7 +1905,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>46075</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2025,7 +1921,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.65</v>
+        <v>44.39</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2035,11 +1931,11 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46130</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2047,25 +1943,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47.17</v>
+        <v>40.39</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46187</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2077,7 +1973,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42.92</v>
+        <v>40.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2087,11 +1983,11 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46208</v>
+        <v>46033</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小6</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2099,11 +1995,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>44.13</v>
+        <v>39.07</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2113,25 +2009,155 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
+        <v>46074</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小6</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
         <v>46313</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小6</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
